--- a/OUTPUT/direct_D5ALN0_Rhodobacter_capsulatus_SB_1003.xlsx
+++ b/OUTPUT/direct_D5ALN0_Rhodobacter_capsulatus_SB_1003.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0002</v>
+        <v>0.0003998400639744102</v>
       </c>
     </row>
   </sheetData>
